--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ga_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_ga_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -911,7 +911,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="n">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="inlineStr"/>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="n">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="inlineStr"/>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="inlineStr"/>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="inlineStr"/>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="inlineStr"/>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="inlineStr"/>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3613,7 +3613,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="inlineStr"/>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="inlineStr"/>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="inlineStr"/>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="inlineStr"/>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>12-11-2021 08:30</t>
+          <t>2021-12-11 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="n">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="n">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>19-05-2021 08:30</t>
+          <t>2021-05-19 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="n">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="n">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="n">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7326,7 +7326,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>17-05-2021 08:30</t>
+          <t>2021-05-17 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -8001,7 +8001,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8195,7 +8195,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>15-12-2021 08:30</t>
+          <t>2021-12-15 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8583,7 +8583,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="n">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>19-05-2021 08:30</t>
+          <t>2021-05-19 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="n">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>08-06-2021 08:30</t>
+          <t>2021-08-06 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10218,7 +10218,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>09-08-2021 08:30</t>
+          <t>2021-09-08 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>08-11-2021 08:30</t>
+          <t>2021-08-11 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10693,7 +10693,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11835,7 +11835,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -12029,7 +12029,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -12126,7 +12126,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12320,7 +12320,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12514,7 +12514,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12805,7 +12805,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="n">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="n">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>01-06-2021 08:30</t>
+          <t>2021-01-06 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="n">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>02-07-2021 08:30</t>
+          <t>2021-02-07 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="n">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>01-09-2021 08:30</t>
+          <t>2021-01-09 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>01-10-2021 08:30</t>
+          <t>2021-01-10 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="n">
@@ -13852,7 +13852,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="n">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -14135,7 +14135,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -14228,7 +14228,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14321,7 +14321,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14507,7 +14507,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14600,7 +14600,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>11-05-2021 08:30</t>
+          <t>2021-11-05 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -15075,7 +15075,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15170,7 +15170,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15265,7 +15265,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="n">
@@ -15360,7 +15360,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="n">
@@ -15455,7 +15455,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="n">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="n">
@@ -15645,7 +15645,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="n">
@@ -15740,7 +15740,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15837,7 +15837,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15934,7 +15934,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>16-04-2021 08:30</t>
+          <t>2021-04-16 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>21-05-2021 08:30</t>
+          <t>2021-05-21 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -16225,7 +16225,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -16322,7 +16322,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>12-07-2021 08:30</t>
+          <t>2021-12-07 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="inlineStr"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -16516,7 +16516,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>13-09-2021 08:30</t>
+          <t>2021-09-13 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>11-10-2021 08:30</t>
+          <t>2021-11-10 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>09-11-2021 08:30</t>
+          <t>2021-09-11 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>13-12-2021 08:30</t>
+          <t>2021-12-13 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -17001,7 +17001,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -17098,7 +17098,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -17195,7 +17195,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17389,7 +17389,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17486,7 +17486,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17583,7 +17583,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17680,7 +17680,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17777,7 +17777,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17874,7 +17874,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17971,7 +17971,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -18068,7 +18068,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -18262,7 +18262,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18359,7 +18359,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18456,7 +18456,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="inlineStr"/>
@@ -18553,7 +18553,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18650,7 +18650,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18844,7 +18844,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18941,7 +18941,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -19038,7 +19038,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -19135,7 +19135,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -19232,7 +19232,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -19325,7 +19325,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19418,7 +19418,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19511,7 +19511,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="n">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="n">
@@ -19701,7 +19701,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="n">
@@ -19796,7 +19796,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="n">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="n">
@@ -19986,7 +19986,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="n">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="n">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="n">
@@ -20271,7 +20271,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="n">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="n">
@@ -20461,7 +20461,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="n">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20649,7 +20649,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20835,7 +20835,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20928,7 +20928,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -21021,7 +21021,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -21114,7 +21114,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -21207,7 +21207,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -21300,7 +21300,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21393,7 +21393,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21486,7 +21486,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21579,7 +21579,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21672,7 +21672,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21765,7 +21765,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21858,7 +21858,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21951,7 +21951,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -22044,7 +22044,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -22137,7 +22137,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -22230,7 +22230,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="inlineStr"/>
@@ -22323,7 +22323,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="inlineStr"/>
@@ -22416,7 +22416,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="inlineStr"/>
@@ -22509,7 +22509,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="inlineStr"/>
@@ -22602,7 +22602,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="inlineStr"/>
@@ -22695,7 +22695,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="inlineStr"/>
@@ -22788,7 +22788,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22881,7 +22881,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -23067,7 +23067,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -23160,7 +23160,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23253,7 +23253,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23346,7 +23346,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23439,7 +23439,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23532,7 +23532,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="inlineStr"/>
@@ -23625,7 +23625,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="inlineStr"/>
@@ -23718,7 +23718,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="inlineStr"/>
@@ -23811,7 +23811,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23904,7 +23904,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23997,7 +23997,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -24090,7 +24090,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="inlineStr"/>
@@ -24183,7 +24183,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="inlineStr"/>
@@ -24276,7 +24276,7 @@
       </c>
       <c r="S250" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T250" t="inlineStr"/>
@@ -24369,7 +24369,7 @@
       </c>
       <c r="S251" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T251" t="inlineStr"/>
@@ -24462,7 +24462,7 @@
       </c>
       <c r="S252" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T252" t="inlineStr"/>
@@ -24555,7 +24555,7 @@
       </c>
       <c r="S253" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T253" t="inlineStr"/>
@@ -24648,7 +24648,7 @@
       </c>
       <c r="S254" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T254" t="inlineStr"/>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T255" t="inlineStr"/>
@@ -24834,7 +24834,7 @@
       </c>
       <c r="S256" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T256" t="inlineStr"/>
@@ -24927,7 +24927,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T257" t="inlineStr"/>
@@ -25020,7 +25020,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T258" t="inlineStr"/>
@@ -25113,7 +25113,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T259" t="inlineStr"/>
@@ -25206,7 +25206,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T260" t="inlineStr"/>
@@ -25299,7 +25299,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T261" t="inlineStr"/>
@@ -25392,7 +25392,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T262" t="inlineStr"/>
@@ -25485,7 +25485,7 @@
       </c>
       <c r="S263" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T263" t="inlineStr"/>
@@ -25578,7 +25578,7 @@
       </c>
       <c r="S264" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T264" t="inlineStr"/>
@@ -25671,7 +25671,7 @@
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T265" t="inlineStr"/>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T266" t="inlineStr"/>
@@ -25857,7 +25857,7 @@
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T267" t="inlineStr"/>
@@ -25950,7 +25950,7 @@
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T268" t="inlineStr"/>
@@ -26043,7 +26043,7 @@
       </c>
       <c r="S269" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T269" t="inlineStr"/>
@@ -26136,7 +26136,7 @@
       </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T270" t="inlineStr"/>
@@ -26229,7 +26229,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T271" t="inlineStr"/>
@@ -26322,7 +26322,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T272" t="inlineStr"/>
@@ -26415,7 +26415,7 @@
       </c>
       <c r="S273" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T273" t="inlineStr"/>
@@ -26508,7 +26508,7 @@
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T274" t="inlineStr"/>
@@ -26601,7 +26601,7 @@
       </c>
       <c r="S275" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T275" t="inlineStr"/>
@@ -26694,7 +26694,7 @@
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T276" t="inlineStr"/>
@@ -26787,7 +26787,7 @@
       </c>
       <c r="S277" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T277" t="inlineStr"/>
@@ -26880,7 +26880,7 @@
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T278" t="inlineStr"/>
@@ -26973,7 +26973,7 @@
       </c>
       <c r="S279" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T279" t="inlineStr"/>
@@ -27066,7 +27066,7 @@
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T280" t="inlineStr"/>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="S281" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T281" t="inlineStr"/>
@@ -27252,7 +27252,7 @@
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T282" t="n">
@@ -27347,7 +27347,7 @@
       </c>
       <c r="S283" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T283" t="n">
@@ -27442,7 +27442,7 @@
       </c>
       <c r="S284" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T284" t="n">
@@ -27537,7 +27537,7 @@
       </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T285" t="n">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="S286" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T286" t="n">
@@ -27727,7 +27727,7 @@
       </c>
       <c r="S287" t="inlineStr">
         <is>
-          <t>07-06-2021 08:30</t>
+          <t>2021-07-06 08:30:00</t>
         </is>
       </c>
       <c r="T287" t="n">
@@ -27822,7 +27822,7 @@
       </c>
       <c r="S288" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T288" t="n">
@@ -27917,7 +27917,7 @@
       </c>
       <c r="S289" t="inlineStr">
         <is>
-          <t>06-08-2021 08:30</t>
+          <t>2021-06-08 08:30:00</t>
         </is>
       </c>
       <c r="T289" t="n">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>07-09-2021 08:30</t>
+          <t>2021-07-09 08:30:00</t>
         </is>
       </c>
       <c r="T290" t="n">
@@ -28107,7 +28107,7 @@
       </c>
       <c r="S291" t="inlineStr">
         <is>
-          <t>06-10-2021 08:30</t>
+          <t>2021-06-10 08:30:00</t>
         </is>
       </c>
       <c r="T291" t="n">
@@ -28202,7 +28202,7 @@
       </c>
       <c r="S292" t="inlineStr">
         <is>
-          <t>05-11-2021 08:30</t>
+          <t>2021-05-11 08:30:00</t>
         </is>
       </c>
       <c r="T292" t="n">
@@ -28297,7 +28297,7 @@
       </c>
       <c r="S293" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T293" t="n">
@@ -28392,7 +28392,7 @@
       </c>
       <c r="S294" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T294" t="n">
@@ -28487,7 +28487,7 @@
       </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T295" t="n">
@@ -28582,7 +28582,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T296" t="n">
@@ -28677,7 +28677,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T297" t="n">
@@ -28772,7 +28772,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T298" t="n">
@@ -28867,7 +28867,7 @@
       </c>
       <c r="S299" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T299" t="n">
@@ -28962,7 +28962,7 @@
       </c>
       <c r="S300" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T300" t="n">
@@ -29057,7 +29057,7 @@
       </c>
       <c r="S301" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T301" t="n">
@@ -29152,7 +29152,7 @@
       </c>
       <c r="S302" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T302" t="n">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T303" t="n">
@@ -29342,7 +29342,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T304" t="n">
@@ -29437,7 +29437,7 @@
       </c>
       <c r="S305" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T305" t="n">
@@ -29532,7 +29532,7 @@
       </c>
       <c r="S306" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T306" t="n">
@@ -29627,7 +29627,7 @@
       </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T307" t="n">
@@ -29722,7 +29722,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T308" t="n">
@@ -29817,7 +29817,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T309" t="n">
@@ -29912,7 +29912,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T310" t="n">
@@ -30007,7 +30007,7 @@
       </c>
       <c r="S311" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T311" t="n">
@@ -30102,7 +30102,7 @@
       </c>
       <c r="S312" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T312" t="n">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="S313" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T313" t="n">
@@ -30292,7 +30292,7 @@
       </c>
       <c r="S314" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T314" t="n">
@@ -30387,7 +30387,7 @@
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T315" t="inlineStr"/>
@@ -30480,7 +30480,7 @@
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T316" t="inlineStr"/>
@@ -30573,7 +30573,7 @@
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T317" t="inlineStr"/>
@@ -30666,7 +30666,7 @@
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T318" t="inlineStr"/>
@@ -30763,7 +30763,7 @@
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T319" t="inlineStr"/>
@@ -30860,7 +30860,7 @@
       </c>
       <c r="S320" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T320" t="inlineStr"/>
@@ -30957,7 +30957,7 @@
       </c>
       <c r="S321" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T321" t="inlineStr"/>
@@ -31054,7 +31054,7 @@
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T322" t="inlineStr"/>
@@ -31151,7 +31151,7 @@
       </c>
       <c r="S323" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T323" t="inlineStr"/>
@@ -31248,7 +31248,7 @@
       </c>
       <c r="S324" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T324" t="inlineStr"/>
@@ -31345,7 +31345,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>03-08-2021 08:30</t>
+          <t>2021-03-08 08:30:00</t>
         </is>
       </c>
       <c r="T325" t="inlineStr"/>
@@ -31442,7 +31442,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>03-09-2021 08:30</t>
+          <t>2021-03-09 08:30:00</t>
         </is>
       </c>
       <c r="T326" t="inlineStr"/>
@@ -31539,7 +31539,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T327" t="inlineStr"/>
@@ -31636,7 +31636,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>02-11-2021 08:30</t>
+          <t>2021-02-11 08:30:00</t>
         </is>
       </c>
       <c r="T328" t="inlineStr"/>
@@ -31733,7 +31733,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>06-12-2021 08:30</t>
+          <t>2021-06-12 08:30:00</t>
         </is>
       </c>
       <c r="T329" t="inlineStr"/>
@@ -31830,7 +31830,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T330" t="inlineStr"/>
@@ -31927,7 +31927,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T331" t="inlineStr"/>
@@ -32024,7 +32024,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T332" t="inlineStr"/>
@@ -32121,7 +32121,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T333" t="inlineStr"/>
@@ -32218,7 +32218,7 @@
       </c>
       <c r="S334" t="inlineStr">
         <is>
-          <t>05-05-2021 08:30</t>
+          <t>2021-05-05 08:30:00</t>
         </is>
       </c>
       <c r="T334" t="inlineStr"/>
@@ -32315,7 +32315,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>04-06-2021 08:30</t>
+          <t>2021-04-06 08:30:00</t>
         </is>
       </c>
       <c r="T335" t="inlineStr"/>
@@ -32412,7 +32412,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T336" t="inlineStr"/>
@@ -32509,7 +32509,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>16-08-2021 08:30</t>
+          <t>2021-08-16 08:30:00</t>
         </is>
       </c>
       <c r="T337" t="inlineStr"/>
@@ -32606,7 +32606,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T338" t="inlineStr"/>
@@ -32703,7 +32703,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T339" t="inlineStr"/>
@@ -32800,7 +32800,7 @@
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>03-11-2021 08:30</t>
+          <t>2021-03-11 08:30:00</t>
         </is>
       </c>
       <c r="T340" t="inlineStr"/>
@@ -32897,7 +32897,7 @@
       </c>
       <c r="S341" t="inlineStr">
         <is>
-          <t>07-12-2021 08:30</t>
+          <t>2021-07-12 08:30:00</t>
         </is>
       </c>
       <c r="T341" t="inlineStr"/>
@@ -32994,7 +32994,7 @@
       </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T342" t="inlineStr"/>
@@ -33091,7 +33091,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T343" t="inlineStr"/>
@@ -33188,7 +33188,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T344" t="inlineStr"/>
@@ -33285,7 +33285,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T345" t="inlineStr"/>
@@ -33382,7 +33382,7 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
-          <t>12-05-2021 08:30</t>
+          <t>2021-12-05 08:30:00</t>
         </is>
       </c>
       <c r="T346" t="inlineStr"/>
@@ -33479,7 +33479,7 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>09-06-2021 08:30</t>
+          <t>2021-09-06 08:30:00</t>
         </is>
       </c>
       <c r="T347" t="inlineStr"/>
@@ -33576,7 +33576,7 @@
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>13-07-2021 08:30</t>
+          <t>2021-07-13 08:30:00</t>
         </is>
       </c>
       <c r="T348" t="inlineStr"/>
@@ -33673,7 +33673,7 @@
       </c>
       <c r="S349" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T349" t="inlineStr"/>
@@ -33770,7 +33770,7 @@
       </c>
       <c r="S350" t="inlineStr">
         <is>
-          <t>15-09-2021 08:30</t>
+          <t>2021-09-15 08:30:00</t>
         </is>
       </c>
       <c r="T350" t="inlineStr"/>
@@ -33867,7 +33867,7 @@
       </c>
       <c r="S351" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T351" t="inlineStr"/>
@@ -33964,7 +33964,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>14-12-2021 08:30</t>
+          <t>2021-12-14 08:30:00</t>
         </is>
       </c>
       <c r="T352" t="inlineStr"/>
@@ -34061,7 +34061,7 @@
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T353" t="n">
@@ -34160,7 +34160,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>08-10-2021 08:30</t>
+          <t>2021-08-10 08:30:00</t>
         </is>
       </c>
       <c r="T354" t="n">
@@ -34261,7 +34261,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T355" t="n">
@@ -34362,7 +34362,7 @@
       </c>
       <c r="S356" t="inlineStr">
         <is>
-          <t>07-04-2021 08:30</t>
+          <t>2021-07-04 08:30:00</t>
         </is>
       </c>
       <c r="T356" t="n">
@@ -34463,7 +34463,7 @@
       </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T357" t="n">
@@ -34564,7 +34564,7 @@
       </c>
       <c r="S358" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T358" t="n">
@@ -34663,7 +34663,7 @@
       </c>
       <c r="S359" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T359" t="n">
@@ -34762,7 +34762,7 @@
       </c>
       <c r="S360" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T360" t="n">
@@ -34863,7 +34863,7 @@
       </c>
       <c r="S361" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T361" t="inlineStr"/>
@@ -34956,7 +34956,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T362" t="inlineStr"/>
@@ -35049,7 +35049,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T363" t="inlineStr"/>
@@ -35142,7 +35142,7 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T364" t="inlineStr"/>
@@ -35235,7 +35235,7 @@
       </c>
       <c r="S365" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T365" t="inlineStr"/>
@@ -35328,7 +35328,7 @@
       </c>
       <c r="S366" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T366" t="inlineStr"/>
